--- a/Result/checksun_type/電信服務業.xlsx
+++ b/Result/checksun_type/電信服務業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>42.55</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>42.6</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>41.46</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>41.46</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>2767.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3043.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>3043.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>10093.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>5362.4</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>5362.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1010.262975570905</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>2767</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2767.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>42.73999999999999</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>41.42</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>41.42</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2040.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>3751.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>3751.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>10263.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>5439.54</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>5439.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-806.2180643579304</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2040</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>43.22</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>42.4</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>41.4</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2843.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>7527.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>7527</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>10587.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>5531.16</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>5531.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-408.0389746123274</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2843</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2843.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>43.68</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>42.32</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>41.38</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>41.38</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>4645.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>8850.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>8850</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>11384.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>5680.18</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>5680.18</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>89.32540268897355</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>4645</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4645.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>44.29</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>42.22</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>41.37</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>2921.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>10771.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>10771.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>13133.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>5760.5</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>5760.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>603.5843201662283</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>2921</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2921.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>44.69</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>41.33</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>41.33</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>6307.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>17143.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>17143.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>13297.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>5823.24</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>5823.24</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1501.397619413508</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>6307</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>6307.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>44.52</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>41.94</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>41.3</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>41.3</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>20919.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>16774.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>16774.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>13033.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>5739.88</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>5739.88</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>2367.580989073429</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>20919</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>20919.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>44.02</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>41.77</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>41.24</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>41.24</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>9458.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>13648.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>13648</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>11284.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>5386.6</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>5386.6</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>1954.857910406408</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>9458</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>9458.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>41.18</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>41.18</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>14252.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>13919.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>13919</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>10532.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>5296.48</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>5296.48</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>2523.401444081863</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>14252</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>14252.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>43.07</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>41.36</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>41.12</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>41.12</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>34781.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>15494.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>15494.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>9420.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>5066.56</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>5066.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>2731.842154901018</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>34781</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>34781.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>42.25000000000001</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>41.06</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>4464.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>9451.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>9451.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>6642.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>4486.98</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>4486.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>732.5130933962018</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>4464</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>4464.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>50.17</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>50.7</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>50.61</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>50.61</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>9868.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>6975.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>6975.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>10189.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>14118.6</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>14118.6</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-2153.24001522178</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>9868</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>9868.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>49.86</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>50.62</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>50.6</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>4788.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>6794.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>6794.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>11280.1</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>14158.66</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>14158.66</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-2402.794357657396</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>4788</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>4788.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>49.83</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>50.64</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>50.64</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>3582.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>7863.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>7863</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>14779.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>14269.36</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>14269.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-2129.200762649085</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>3582</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>3582.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>49.92</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>50.61</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>50.68</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>50.61</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>50.68</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>10464.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>10309.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>10309.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>22214.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>14444.32</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>14444.32</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-1533.095599685457</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>10464</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>10464.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>50.27999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>50.64</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>50.71</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>50.71</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>6175.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>12144.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>12144.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>22806.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>14498.7</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>14498.7</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-1364.120524034368</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>6175</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>6175.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>50.68</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>50.68</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>50.73</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>50.73</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>8964.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>13403.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>13403.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>23833.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>14574.58</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>14574.58</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-614.4732543887258</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>8964</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>8964.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>51.20999999999999</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>50.7</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>50.76</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>50.76</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>10130.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>15765.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>15765.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>23700.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>14525.78</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>14525.78</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>179.5754613332174</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>10130</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>10130.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>51.6</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>50.7</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>50.78</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>50.78</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>15813.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>21696.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>21696</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>23345.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>14450.14</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>14450.14</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>1182.588788745525</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>15813</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>15813.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>52.02</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>50.66</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>50.78</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>50.78</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>19642.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>34118.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>34118.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>22718.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>14309.56</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>14309.56</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>1964.336799736477</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>19642</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>19642.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>52.06</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>50.55</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>50.76</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>50.76</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>12468.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>33468.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>33468</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>21931.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>14204.04</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>14204.04</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>2600.714786875818</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>12468</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>12468.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>51.84</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>50.38</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>50.75</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>50.75</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>20775.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>34262.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>34262.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>21820.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>14315.36</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>14315.36</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>4185.586383257887</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>20775</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>20775.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>23.44</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>23.56</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>23.59</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>23.59</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>3372838.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>6634679.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>6634679.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>4993357.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>2943934.1</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>2943934.1</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>137565.8245880157</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>3372838</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>3372838.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>23.41</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>23.59</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>23.59</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>2262057.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>6355148.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>6355148.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>4860961.6</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>2951760.98</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>2951760.98</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>280733.560738245</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>2262057</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>2262057.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>23.42</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>23.56</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>23.59</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>23.59</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1742347.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>6350518.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>6350518.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>5181423.9</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>2985729.36</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>2985729.36</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>594244.9494979214</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1742347</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1742347.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>23.46</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>23.58</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>23.6</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>6762846.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>6840550.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>6840550.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>5203374.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>2981768.22</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>2981768.22</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>1076578.542386819</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>6762846</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>6762846.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>23.53</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>23.6</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>19033310.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>6068420.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>6068420</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>4833241.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>2912218.46</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>2912218.46</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>1189266.691428571</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>19033310</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>19033310.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>23.57</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>23.62</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>23.61</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>23.61</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1975182.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>3352035.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>3352035.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>3450809.0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>2553703.5</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>2553703.5</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-6916.620348517783</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1975182</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1975182.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>23.64</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>23.61</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>23.61</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>2238909.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>3366774.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>3366774.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>3709061.3</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>2557186.52</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>2557186.52</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>112153.6706966604</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>2238909</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>2238909.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>23.7</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>23.65</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>23.6</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>4192504.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>4012329.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>4012329</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>3744307.6</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2595866.38</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2595866.38</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>249992.1339506051</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>4192504</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>4192504.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>23.72</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>23.65</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>23.6</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>2902195.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>3566198.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>3566198.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>3672682.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2577075.02</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2577075.02</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>228662.1838151477</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>2902195</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>2902195.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>23.7</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>23.59</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>23.59</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>5451387.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>3598063.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>3598063.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>3492519.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2608636.76</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>2608636.76</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>328271.7127710967</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>5451387</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>5451387.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>23.69</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>23.6</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>2048879.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>3549582.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>3549582.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>3189538.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>2588847.5</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>2588847.5</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>185719.3358234847</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>2048879</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>2048879.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>90.96000000000001</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>92.54</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>90.67</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>92.54000000000001</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>90.67</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>656136060.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>879778105.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>879778105.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>759103788.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>626633799.62</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>626633799.62</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>65093311.48577023</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>656136060</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>656136060.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>91.54</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>92.72</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>90.57</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>90.56999999999999</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1277054541.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>853766186.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>853766186</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>757688034.0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>619862538.14</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>619862538.14</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>90628052.82458293</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1277054541</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1277054541.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>92.14000000000001</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>92.9</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>90.48</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>90.48</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>1118083203.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>752575101.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>752575101.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>673693726.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>599180326.5</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>599180326.5</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>57342558.45772314</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>1118083203</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>1118083203.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>91.9</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>92.88</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>90.31</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>92.88</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>90.31</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>1012560565.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>629611702.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>629611702.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>622178080.5</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>581361470.74</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>581361470.74</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>24776547.06014764</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>1012560565</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>1012560565.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>91.92</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>93.04</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>90.17</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>93.04000000000001</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>90.17</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>335056158.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>521875595.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>521875595.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>604487415.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>564710067.64</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>564710067.64</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-11325206.11710846</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>335056158</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>335056158.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>91.7</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>93.12</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>90</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>526076463.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>638429471.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>638429471.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>622450286.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>561107105.36</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>561107105.36</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>10095090.31242251</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>526076463</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>526076463.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>92.17999999999999</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>93.18</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>89.86</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>93.18000000000001</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>89.86</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>771099119.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>661609882.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>661609882</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>616022574.0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>553432803.96</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>553432803.96</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>19868513.59345174</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>771099119</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>771099119.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>92.5</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>93.22</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>89.71</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>89.70999999999999</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>503266206.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>594812352.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>594812352.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>605996751.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>541932423.36</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>541932423.36</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>6868529.652298689</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>503266206</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>503266206.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>93.0</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>93.27</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>89.57</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>93.27</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>89.56999999999999</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>473880033.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>614744458.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>614744458.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>602571401.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>535586548.1</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>535586548.1</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>16748202.92735505</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>473880033</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>473880033.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>93.79999999999998</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>93.32</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>89.43</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>93.31999999999999</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>89.43000000000001</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>917825536.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>687099235.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>687099235.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>602619708.7</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>530761237.22</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>530761237.22</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>33412390.32288718</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>917825536</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>917825536.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>94.18</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>93.34</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>89.28</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>89.28</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>641978516.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>606471102.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>606471102.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>569007365.5</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>521134872.04</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>521134872.04</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>8459483.054972887</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>641978516</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>641978516.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>107.9</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>109.02</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>108.98</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>109.02</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>108.98</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>770097003.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>751539747.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>751539747.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>759974757.6</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>763014348.66</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>763014348.66</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>18359211.22418582</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>770097003</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>770097003.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>107.4</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>109.12</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>108.93</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>109.12</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>108.93</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>921046320.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>733253377.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>733253377.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>763864417.0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>754372042.06</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>754372042.0599999</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>20495989.58930314</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>921046320</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>921046320.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>107.3</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>109.32</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>108.92</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>109.32</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>108.92</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>1048990478.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>701558990.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>701558990.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>712169678.8</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>747101907.64</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>747101907.64</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>6643389.375567198</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>1048990478</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>1048990478.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>107.3</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>109.48</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>108.91</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>109.48</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>108.91</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>571604984.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>624443507.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>624443507.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>670629396.1</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>733193103.42</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>733193103.42</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-27091606.05032587</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>571604984</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>571604984.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>107.6</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>109.75</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>108.91</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>108.91</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>445959954.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>587309566.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>587309566</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>700776419.3</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>731219490.3</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>731219490.3</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-23168453.51409006</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>445959954</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>445959954.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>107.7</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>109.95</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>108.87</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>108.87</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>678665150.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>768409767.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>768409767.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>723248680.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>728983710.58</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>728983710.58</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-3274537.622535706</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>678665150</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>678665150.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>108.6</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>110.18</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>108.87</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>110.18</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>108.87</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>762574386.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>794475456.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>794475456.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>711399275.8</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>720921931.02</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>720921931.02</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>329590.4233468771</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>762574386</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>762574386.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>109.2</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>110.4</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>108.86</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>108.86</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>663413062.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>722780367.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>722780367.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>729323162.8</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>711765140.64</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>711765140.64</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-3523701.597654939</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>663413062</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>663413062.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>109.7</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>110.58</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>108.84</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>110.58</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>108.84</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>385935278.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>716815285.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>716815285</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>730647678.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>705287396.56</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>705287396.5599999</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>1721869.572258949</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>385935278</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>385935278.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>110.2</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>110.65</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>108.8</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>108.8</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>1351460961.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>814243272.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>814243272.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>763261651.9</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>704591266.12</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>704591266.12</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>38883809.90169811</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>1351460961</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>1351460961.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>110.5</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>110.68</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>108.76</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>110.68</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>108.76</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>808993597.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>678087594.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>678087594.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>725418450.0</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>692623321.38</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>692623321.38</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-12865591.73130643</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>808993597</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>808993597.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>131.5</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>131.6</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>132.66</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>132.66</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>725286524.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>1275615380.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>1275615380.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>960082637.8</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>882449748.66</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>882449748.66</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>70594831.6741656</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>725286524</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>725286524.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>131.4</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>131.65</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>132.73</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>131.65</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>132.73</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>1001773528.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1251088824.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1251088824.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>948395506.6</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>884332649.12</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>884332649.12</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>118034321.2080046</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>1001773528</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>1001773528.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>131.4</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>131.7</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>132.82</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>132.82</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>3005429631.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1209605479.6</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1209605479.6</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>896034230.9</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>874724884.14</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>874724884.14</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>151965901.4989175</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>3005429631</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>3005429631.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>131.4</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>131.7</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>132.89</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>132.89</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1092637429.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>751048540.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>751048540.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>639093116.1</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>829154473.82</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>829154473.8200001</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-19665205.6033113</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1092637429</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1092637429.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>131.4</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>131.82</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>132.95</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>131.82</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>132.95</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>552949791.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>628961706.0</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>628961706</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>629868978.7</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>817253180.6</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>817253180.6</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-59208151.04923415</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>552949791</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>552949791.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>131.3</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>131.9</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>133</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>602653744.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>644549895.0</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>644549895</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>658688448.7</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>817920357.98</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>817920357.98</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-55759820.79165125</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>602653744</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>602653744.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>131.6</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>132.02</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>133.09</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>132.02</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>133.09</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>794356803.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>645702188.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>645702188.6</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>679988453.6</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>817224899.94</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>817224899.9400001</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-54167636.07397389</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>794356803</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>794356803.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>131.8</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>132.12</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>133.15</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>132.12</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>133.15</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>712644935.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>582462982.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>582462982.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>720766131.3</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>814664800.44</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>814664800.4400001</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-70498141.51036417</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>712644935</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>712644935.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>132.0</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>132.18</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>133.21</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>132.18</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>133.21</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>482203257.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>527137691.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>527137691.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>745657320.2</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>810804102.16</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>810804102.16</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-82554801.2226944</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>482203257</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>482203257.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>132.2</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>132.2</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>133.26</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>133.26</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>630890736.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>630776251.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>630776251.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>770851227.8</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>812312457.78</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>812312457.78</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-72140035.26806986</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>630890736</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>630890736.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>132.2</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>132.2</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>133.28</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>133.28</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>608415212.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>672827002.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>672827002.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>908606071.4</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>820004964.16</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>820004964.16</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-70616169.68046093</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>608415212</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>608415212.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
